--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_24mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_24mo.xlsx
@@ -1007,20 +1007,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -1047,15 +1082,15 @@
       <c r="AJ2" s="21" t="n"/>
       <c r="AK2" s="21" t="n"/>
       <c r="AL2" s="24">
-        <f>SUM(M2:AJ2)</f>
+        <f>H2+SUM(M2:AJ2)</f>
         <v/>
       </c>
       <c r="AM2" s="24">
-        <f>I2-AL2</f>
+        <f>I2-H2-SUM(M2:AJ2)</f>
         <v/>
       </c>
       <c r="AN2" s="25">
-        <f>IF(I2=0,"",AL2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:AJ2))/I2)</f>
         <v/>
       </c>
       <c r="AO2" s="26" t="n"/>
@@ -1108,15 +1143,15 @@
       <c r="AJ3" s="21" t="n"/>
       <c r="AK3" s="21" t="n"/>
       <c r="AL3" s="24">
-        <f>SUM(M3:AJ3)</f>
+        <f>H3+SUM(M3:AJ3)</f>
         <v/>
       </c>
       <c r="AM3" s="24">
-        <f>I3-AL3</f>
+        <f>I3-H3-SUM(M3:AJ3)</f>
         <v/>
       </c>
       <c r="AN3" s="25">
-        <f>IF(I3=0,"",AL3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:AJ3))/I3)</f>
         <v/>
       </c>
       <c r="AO3" s="26" t="n"/>
@@ -1169,15 +1204,15 @@
       <c r="AJ4" s="21" t="n"/>
       <c r="AK4" s="21" t="n"/>
       <c r="AL4" s="24">
-        <f>SUM(M4:AJ4)</f>
+        <f>H4+SUM(M4:AJ4)</f>
         <v/>
       </c>
       <c r="AM4" s="24">
-        <f>I4-AL4</f>
+        <f>I4-H4-SUM(M4:AJ4)</f>
         <v/>
       </c>
       <c r="AN4" s="25">
-        <f>IF(I4=0,"",AL4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:AJ4))/I4)</f>
         <v/>
       </c>
       <c r="AO4" s="26" t="n"/>
@@ -1230,15 +1265,15 @@
       <c r="AJ5" s="21" t="n"/>
       <c r="AK5" s="21" t="n"/>
       <c r="AL5" s="24">
-        <f>SUM(M5:AJ5)</f>
+        <f>H5+SUM(M5:AJ5)</f>
         <v/>
       </c>
       <c r="AM5" s="24">
-        <f>I5-AL5</f>
+        <f>I5-H5-SUM(M5:AJ5)</f>
         <v/>
       </c>
       <c r="AN5" s="25">
-        <f>IF(I5=0,"",AL5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:AJ5))/I5)</f>
         <v/>
       </c>
       <c r="AO5" s="26" t="n"/>
@@ -1291,15 +1326,15 @@
       <c r="AJ6" s="21" t="n"/>
       <c r="AK6" s="21" t="n"/>
       <c r="AL6" s="24">
-        <f>SUM(M6:AJ6)</f>
+        <f>H6+SUM(M6:AJ6)</f>
         <v/>
       </c>
       <c r="AM6" s="24">
-        <f>I6-AL6</f>
+        <f>I6-H6-SUM(M6:AJ6)</f>
         <v/>
       </c>
       <c r="AN6" s="25">
-        <f>IF(I6=0,"",AL6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:AJ6))/I6)</f>
         <v/>
       </c>
       <c r="AO6" s="26" t="n"/>
@@ -1352,15 +1387,15 @@
       <c r="AJ7" s="21" t="n"/>
       <c r="AK7" s="21" t="n"/>
       <c r="AL7" s="24">
-        <f>SUM(M7:AJ7)</f>
+        <f>H7+SUM(M7:AJ7)</f>
         <v/>
       </c>
       <c r="AM7" s="24">
-        <f>I7-AL7</f>
+        <f>I7-H7-SUM(M7:AJ7)</f>
         <v/>
       </c>
       <c r="AN7" s="25">
-        <f>IF(I7=0,"",AL7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:AJ7))/I7)</f>
         <v/>
       </c>
       <c r="AO7" s="26" t="n"/>
@@ -1413,15 +1448,15 @@
       <c r="AJ8" s="21" t="n"/>
       <c r="AK8" s="21" t="n"/>
       <c r="AL8" s="24">
-        <f>SUM(M8:AJ8)</f>
+        <f>H8+SUM(M8:AJ8)</f>
         <v/>
       </c>
       <c r="AM8" s="24">
-        <f>I8-AL8</f>
+        <f>I8-H8-SUM(M8:AJ8)</f>
         <v/>
       </c>
       <c r="AN8" s="25">
-        <f>IF(I8=0,"",AL8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:AJ8))/I8)</f>
         <v/>
       </c>
       <c r="AO8" s="26" t="n"/>
@@ -1474,15 +1509,15 @@
       <c r="AJ9" s="21" t="n"/>
       <c r="AK9" s="21" t="n"/>
       <c r="AL9" s="24">
-        <f>SUM(M9:AJ9)</f>
+        <f>H9+SUM(M9:AJ9)</f>
         <v/>
       </c>
       <c r="AM9" s="24">
-        <f>I9-AL9</f>
+        <f>I9-H9-SUM(M9:AJ9)</f>
         <v/>
       </c>
       <c r="AN9" s="25">
-        <f>IF(I9=0,"",AL9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:AJ9))/I9)</f>
         <v/>
       </c>
       <c r="AO9" s="26" t="n"/>
@@ -1535,15 +1570,15 @@
       <c r="AJ10" s="21" t="n"/>
       <c r="AK10" s="21" t="n"/>
       <c r="AL10" s="24">
-        <f>SUM(M10:AJ10)</f>
+        <f>H10+SUM(M10:AJ10)</f>
         <v/>
       </c>
       <c r="AM10" s="24">
-        <f>I10-AL10</f>
+        <f>I10-H10-SUM(M10:AJ10)</f>
         <v/>
       </c>
       <c r="AN10" s="25">
-        <f>IF(I10=0,"",AL10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:AJ10))/I10)</f>
         <v/>
       </c>
       <c r="AO10" s="26" t="n"/>
@@ -1596,15 +1631,15 @@
       <c r="AJ11" s="21" t="n"/>
       <c r="AK11" s="21" t="n"/>
       <c r="AL11" s="24">
-        <f>SUM(M11:AJ11)</f>
+        <f>H11+SUM(M11:AJ11)</f>
         <v/>
       </c>
       <c r="AM11" s="24">
-        <f>I11-AL11</f>
+        <f>I11-H11-SUM(M11:AJ11)</f>
         <v/>
       </c>
       <c r="AN11" s="25">
-        <f>IF(I11=0,"",AL11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:AJ11))/I11)</f>
         <v/>
       </c>
       <c r="AO11" s="26" t="n"/>
@@ -1657,15 +1692,15 @@
       <c r="AJ12" s="21" t="n"/>
       <c r="AK12" s="21" t="n"/>
       <c r="AL12" s="24">
-        <f>SUM(M12:AJ12)</f>
+        <f>H12+SUM(M12:AJ12)</f>
         <v/>
       </c>
       <c r="AM12" s="24">
-        <f>I12-AL12</f>
+        <f>I12-H12-SUM(M12:AJ12)</f>
         <v/>
       </c>
       <c r="AN12" s="25">
-        <f>IF(I12=0,"",AL12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:AJ12))/I12)</f>
         <v/>
       </c>
       <c r="AO12" s="26" t="n"/>
@@ -1718,15 +1753,15 @@
       <c r="AJ13" s="21" t="n"/>
       <c r="AK13" s="21" t="n"/>
       <c r="AL13" s="24">
-        <f>SUM(M13:AJ13)</f>
+        <f>H13+SUM(M13:AJ13)</f>
         <v/>
       </c>
       <c r="AM13" s="24">
-        <f>I13-AL13</f>
+        <f>I13-H13-SUM(M13:AJ13)</f>
         <v/>
       </c>
       <c r="AN13" s="25">
-        <f>IF(I13=0,"",AL13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:AJ13))/I13)</f>
         <v/>
       </c>
       <c r="AO13" s="26" t="n"/>
@@ -1779,15 +1814,15 @@
       <c r="AJ14" s="21" t="n"/>
       <c r="AK14" s="21" t="n"/>
       <c r="AL14" s="24">
-        <f>SUM(M14:AJ14)</f>
+        <f>H14+SUM(M14:AJ14)</f>
         <v/>
       </c>
       <c r="AM14" s="24">
-        <f>I14-AL14</f>
+        <f>I14-H14-SUM(M14:AJ14)</f>
         <v/>
       </c>
       <c r="AN14" s="25">
-        <f>IF(I14=0,"",AL14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:AJ14))/I14)</f>
         <v/>
       </c>
       <c r="AO14" s="26" t="n"/>
@@ -1840,15 +1875,15 @@
       <c r="AJ15" s="21" t="n"/>
       <c r="AK15" s="21" t="n"/>
       <c r="AL15" s="24">
-        <f>SUM(M15:AJ15)</f>
+        <f>H15+SUM(M15:AJ15)</f>
         <v/>
       </c>
       <c r="AM15" s="24">
-        <f>I15-AL15</f>
+        <f>I15-H15-SUM(M15:AJ15)</f>
         <v/>
       </c>
       <c r="AN15" s="25">
-        <f>IF(I15=0,"",AL15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:AJ15))/I15)</f>
         <v/>
       </c>
       <c r="AO15" s="26" t="n"/>
@@ -1901,15 +1936,15 @@
       <c r="AJ16" s="21" t="n"/>
       <c r="AK16" s="21" t="n"/>
       <c r="AL16" s="24">
-        <f>SUM(M16:AJ16)</f>
+        <f>H16+SUM(M16:AJ16)</f>
         <v/>
       </c>
       <c r="AM16" s="24">
-        <f>I16-AL16</f>
+        <f>I16-H16-SUM(M16:AJ16)</f>
         <v/>
       </c>
       <c r="AN16" s="25">
-        <f>IF(I16=0,"",AL16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:AJ16))/I16)</f>
         <v/>
       </c>
       <c r="AO16" s="26" t="n"/>
@@ -1962,15 +1997,15 @@
       <c r="AJ17" s="21" t="n"/>
       <c r="AK17" s="21" t="n"/>
       <c r="AL17" s="24">
-        <f>SUM(M17:AJ17)</f>
+        <f>H17+SUM(M17:AJ17)</f>
         <v/>
       </c>
       <c r="AM17" s="24">
-        <f>I17-AL17</f>
+        <f>I17-H17-SUM(M17:AJ17)</f>
         <v/>
       </c>
       <c r="AN17" s="25">
-        <f>IF(I17=0,"",AL17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:AJ17))/I17)</f>
         <v/>
       </c>
       <c r="AO17" s="26" t="n"/>
@@ -2023,15 +2058,15 @@
       <c r="AJ18" s="21" t="n"/>
       <c r="AK18" s="21" t="n"/>
       <c r="AL18" s="24">
-        <f>SUM(M18:AJ18)</f>
+        <f>H18+SUM(M18:AJ18)</f>
         <v/>
       </c>
       <c r="AM18" s="24">
-        <f>I18-AL18</f>
+        <f>I18-H18-SUM(M18:AJ18)</f>
         <v/>
       </c>
       <c r="AN18" s="25">
-        <f>IF(I18=0,"",AL18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:AJ18))/I18)</f>
         <v/>
       </c>
       <c r="AO18" s="26" t="n"/>
@@ -2084,15 +2119,15 @@
       <c r="AJ19" s="21" t="n"/>
       <c r="AK19" s="21" t="n"/>
       <c r="AL19" s="24">
-        <f>SUM(M19:AJ19)</f>
+        <f>H19+SUM(M19:AJ19)</f>
         <v/>
       </c>
       <c r="AM19" s="24">
-        <f>I19-AL19</f>
+        <f>I19-H19-SUM(M19:AJ19)</f>
         <v/>
       </c>
       <c r="AN19" s="25">
-        <f>IF(I19=0,"",AL19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:AJ19))/I19)</f>
         <v/>
       </c>
       <c r="AO19" s="26" t="n"/>
@@ -2145,15 +2180,15 @@
       <c r="AJ20" s="21" t="n"/>
       <c r="AK20" s="21" t="n"/>
       <c r="AL20" s="24">
-        <f>SUM(M20:AJ20)</f>
+        <f>H20+SUM(M20:AJ20)</f>
         <v/>
       </c>
       <c r="AM20" s="24">
-        <f>I20-AL20</f>
+        <f>I20-H20-SUM(M20:AJ20)</f>
         <v/>
       </c>
       <c r="AN20" s="25">
-        <f>IF(I20=0,"",AL20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:AJ20))/I20)</f>
         <v/>
       </c>
       <c r="AO20" s="26" t="n"/>
@@ -2206,15 +2241,15 @@
       <c r="AJ21" s="21" t="n"/>
       <c r="AK21" s="21" t="n"/>
       <c r="AL21" s="24">
-        <f>SUM(M21:AJ21)</f>
+        <f>H21+SUM(M21:AJ21)</f>
         <v/>
       </c>
       <c r="AM21" s="24">
-        <f>I21-AL21</f>
+        <f>I21-H21-SUM(M21:AJ21)</f>
         <v/>
       </c>
       <c r="AN21" s="25">
-        <f>IF(I21=0,"",AL21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:AJ21))/I21)</f>
         <v/>
       </c>
       <c r="AO21" s="26" t="n"/>
@@ -2267,15 +2302,15 @@
       <c r="AJ22" s="21" t="n"/>
       <c r="AK22" s="21" t="n"/>
       <c r="AL22" s="24">
-        <f>SUM(M22:AJ22)</f>
+        <f>H22+SUM(M22:AJ22)</f>
         <v/>
       </c>
       <c r="AM22" s="24">
-        <f>I22-AL22</f>
+        <f>I22-H22-SUM(M22:AJ22)</f>
         <v/>
       </c>
       <c r="AN22" s="25">
-        <f>IF(I22=0,"",AL22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:AJ22))/I22)</f>
         <v/>
       </c>
       <c r="AO22" s="26" t="n"/>
@@ -2328,15 +2363,15 @@
       <c r="AJ23" s="21" t="n"/>
       <c r="AK23" s="21" t="n"/>
       <c r="AL23" s="24">
-        <f>SUM(M23:AJ23)</f>
+        <f>H23+SUM(M23:AJ23)</f>
         <v/>
       </c>
       <c r="AM23" s="24">
-        <f>I23-AL23</f>
+        <f>I23-H23-SUM(M23:AJ23)</f>
         <v/>
       </c>
       <c r="AN23" s="25">
-        <f>IF(I23=0,"",AL23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:AJ23))/I23)</f>
         <v/>
       </c>
       <c r="AO23" s="26" t="n"/>
@@ -2389,15 +2424,15 @@
       <c r="AJ24" s="21" t="n"/>
       <c r="AK24" s="21" t="n"/>
       <c r="AL24" s="24">
-        <f>SUM(M24:AJ24)</f>
+        <f>H24+SUM(M24:AJ24)</f>
         <v/>
       </c>
       <c r="AM24" s="24">
-        <f>I24-AL24</f>
+        <f>I24-H24-SUM(M24:AJ24)</f>
         <v/>
       </c>
       <c r="AN24" s="25">
-        <f>IF(I24=0,"",AL24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:AJ24))/I24)</f>
         <v/>
       </c>
       <c r="AO24" s="26" t="n"/>
@@ -2450,15 +2485,15 @@
       <c r="AJ25" s="21" t="n"/>
       <c r="AK25" s="21" t="n"/>
       <c r="AL25" s="24">
-        <f>SUM(M25:AJ25)</f>
+        <f>H25+SUM(M25:AJ25)</f>
         <v/>
       </c>
       <c r="AM25" s="24">
-        <f>I25-AL25</f>
+        <f>I25-H25-SUM(M25:AJ25)</f>
         <v/>
       </c>
       <c r="AN25" s="25">
-        <f>IF(I25=0,"",AL25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:AJ25))/I25)</f>
         <v/>
       </c>
       <c r="AO25" s="26" t="n"/>
@@ -2511,15 +2546,15 @@
       <c r="AJ26" s="21" t="n"/>
       <c r="AK26" s="21" t="n"/>
       <c r="AL26" s="24">
-        <f>SUM(M26:AJ26)</f>
+        <f>H26+SUM(M26:AJ26)</f>
         <v/>
       </c>
       <c r="AM26" s="24">
-        <f>I26-AL26</f>
+        <f>I26-H26-SUM(M26:AJ26)</f>
         <v/>
       </c>
       <c r="AN26" s="25">
-        <f>IF(I26=0,"",AL26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:AJ26))/I26)</f>
         <v/>
       </c>
       <c r="AO26" s="26" t="n"/>
@@ -2572,15 +2607,15 @@
       <c r="AJ27" s="21" t="n"/>
       <c r="AK27" s="21" t="n"/>
       <c r="AL27" s="24">
-        <f>SUM(M27:AJ27)</f>
+        <f>H27+SUM(M27:AJ27)</f>
         <v/>
       </c>
       <c r="AM27" s="24">
-        <f>I27-AL27</f>
+        <f>I27-H27-SUM(M27:AJ27)</f>
         <v/>
       </c>
       <c r="AN27" s="25">
-        <f>IF(I27=0,"",AL27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:AJ27))/I27)</f>
         <v/>
       </c>
       <c r="AO27" s="26" t="n"/>
@@ -2633,15 +2668,15 @@
       <c r="AJ28" s="21" t="n"/>
       <c r="AK28" s="21" t="n"/>
       <c r="AL28" s="24">
-        <f>SUM(M28:AJ28)</f>
+        <f>H28+SUM(M28:AJ28)</f>
         <v/>
       </c>
       <c r="AM28" s="24">
-        <f>I28-AL28</f>
+        <f>I28-H28-SUM(M28:AJ28)</f>
         <v/>
       </c>
       <c r="AN28" s="25">
-        <f>IF(I28=0,"",AL28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:AJ28))/I28)</f>
         <v/>
       </c>
       <c r="AO28" s="26" t="n"/>
@@ -2694,15 +2729,15 @@
       <c r="AJ29" s="21" t="n"/>
       <c r="AK29" s="21" t="n"/>
       <c r="AL29" s="24">
-        <f>SUM(M29:AJ29)</f>
+        <f>H29+SUM(M29:AJ29)</f>
         <v/>
       </c>
       <c r="AM29" s="24">
-        <f>I29-AL29</f>
+        <f>I29-H29-SUM(M29:AJ29)</f>
         <v/>
       </c>
       <c r="AN29" s="25">
-        <f>IF(I29=0,"",AL29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:AJ29))/I29)</f>
         <v/>
       </c>
       <c r="AO29" s="26" t="n"/>
@@ -2755,15 +2790,15 @@
       <c r="AJ30" s="21" t="n"/>
       <c r="AK30" s="21" t="n"/>
       <c r="AL30" s="24">
-        <f>SUM(M30:AJ30)</f>
+        <f>H30+SUM(M30:AJ30)</f>
         <v/>
       </c>
       <c r="AM30" s="24">
-        <f>I30-AL30</f>
+        <f>I30-H30-SUM(M30:AJ30)</f>
         <v/>
       </c>
       <c r="AN30" s="25">
-        <f>IF(I30=0,"",AL30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:AJ30))/I30)</f>
         <v/>
       </c>
       <c r="AO30" s="26" t="n"/>
@@ -2816,15 +2851,15 @@
       <c r="AJ31" s="21" t="n"/>
       <c r="AK31" s="21" t="n"/>
       <c r="AL31" s="24">
-        <f>SUM(M31:AJ31)</f>
+        <f>H31+SUM(M31:AJ31)</f>
         <v/>
       </c>
       <c r="AM31" s="24">
-        <f>I31-AL31</f>
+        <f>I31-H31-SUM(M31:AJ31)</f>
         <v/>
       </c>
       <c r="AN31" s="25">
-        <f>IF(I31=0,"",AL31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:AJ31))/I31)</f>
         <v/>
       </c>
       <c r="AO31" s="26" t="n"/>
@@ -2877,15 +2912,15 @@
       <c r="AJ32" s="21" t="n"/>
       <c r="AK32" s="21" t="n"/>
       <c r="AL32" s="24">
-        <f>SUM(M32:AJ32)</f>
+        <f>H32+SUM(M32:AJ32)</f>
         <v/>
       </c>
       <c r="AM32" s="24">
-        <f>I32-AL32</f>
+        <f>I32-H32-SUM(M32:AJ32)</f>
         <v/>
       </c>
       <c r="AN32" s="25">
-        <f>IF(I32=0,"",AL32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:AJ32))/I32)</f>
         <v/>
       </c>
       <c r="AO32" s="26" t="n"/>
@@ -2938,15 +2973,15 @@
       <c r="AJ33" s="21" t="n"/>
       <c r="AK33" s="21" t="n"/>
       <c r="AL33" s="24">
-        <f>SUM(M33:AJ33)</f>
+        <f>H33+SUM(M33:AJ33)</f>
         <v/>
       </c>
       <c r="AM33" s="24">
-        <f>I33-AL33</f>
+        <f>I33-H33-SUM(M33:AJ33)</f>
         <v/>
       </c>
       <c r="AN33" s="25">
-        <f>IF(I33=0,"",AL33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:AJ33))/I33)</f>
         <v/>
       </c>
       <c r="AO33" s="26" t="n"/>
@@ -2999,15 +3034,15 @@
       <c r="AJ34" s="21" t="n"/>
       <c r="AK34" s="21" t="n"/>
       <c r="AL34" s="24">
-        <f>SUM(M34:AJ34)</f>
+        <f>H34+SUM(M34:AJ34)</f>
         <v/>
       </c>
       <c r="AM34" s="24">
-        <f>I34-AL34</f>
+        <f>I34-H34-SUM(M34:AJ34)</f>
         <v/>
       </c>
       <c r="AN34" s="25">
-        <f>IF(I34=0,"",AL34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:AJ34))/I34)</f>
         <v/>
       </c>
       <c r="AO34" s="26" t="n"/>
@@ -3060,15 +3095,15 @@
       <c r="AJ35" s="21" t="n"/>
       <c r="AK35" s="21" t="n"/>
       <c r="AL35" s="24">
-        <f>SUM(M35:AJ35)</f>
+        <f>H35+SUM(M35:AJ35)</f>
         <v/>
       </c>
       <c r="AM35" s="24">
-        <f>I35-AL35</f>
+        <f>I35-H35-SUM(M35:AJ35)</f>
         <v/>
       </c>
       <c r="AN35" s="25">
-        <f>IF(I35=0,"",AL35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:AJ35))/I35)</f>
         <v/>
       </c>
       <c r="AO35" s="26" t="n"/>
@@ -3121,15 +3156,15 @@
       <c r="AJ36" s="21" t="n"/>
       <c r="AK36" s="21" t="n"/>
       <c r="AL36" s="24">
-        <f>SUM(M36:AJ36)</f>
+        <f>H36+SUM(M36:AJ36)</f>
         <v/>
       </c>
       <c r="AM36" s="24">
-        <f>I36-AL36</f>
+        <f>I36-H36-SUM(M36:AJ36)</f>
         <v/>
       </c>
       <c r="AN36" s="25">
-        <f>IF(I36=0,"",AL36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:AJ36))/I36)</f>
         <v/>
       </c>
       <c r="AO36" s="26" t="n"/>
@@ -3182,15 +3217,15 @@
       <c r="AJ37" s="21" t="n"/>
       <c r="AK37" s="21" t="n"/>
       <c r="AL37" s="24">
-        <f>SUM(M37:AJ37)</f>
+        <f>H37+SUM(M37:AJ37)</f>
         <v/>
       </c>
       <c r="AM37" s="24">
-        <f>I37-AL37</f>
+        <f>I37-H37-SUM(M37:AJ37)</f>
         <v/>
       </c>
       <c r="AN37" s="25">
-        <f>IF(I37=0,"",AL37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:AJ37))/I37)</f>
         <v/>
       </c>
       <c r="AO37" s="26" t="n"/>
@@ -3243,15 +3278,15 @@
       <c r="AJ38" s="21" t="n"/>
       <c r="AK38" s="21" t="n"/>
       <c r="AL38" s="24">
-        <f>SUM(M38:AJ38)</f>
+        <f>H38+SUM(M38:AJ38)</f>
         <v/>
       </c>
       <c r="AM38" s="24">
-        <f>I38-AL38</f>
+        <f>I38-H38-SUM(M38:AJ38)</f>
         <v/>
       </c>
       <c r="AN38" s="25">
-        <f>IF(I38=0,"",AL38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:AJ38))/I38)</f>
         <v/>
       </c>
       <c r="AO38" s="26" t="n"/>
@@ -3304,15 +3339,15 @@
       <c r="AJ39" s="21" t="n"/>
       <c r="AK39" s="21" t="n"/>
       <c r="AL39" s="24">
-        <f>SUM(M39:AJ39)</f>
+        <f>H39+SUM(M39:AJ39)</f>
         <v/>
       </c>
       <c r="AM39" s="24">
-        <f>I39-AL39</f>
+        <f>I39-H39-SUM(M39:AJ39)</f>
         <v/>
       </c>
       <c r="AN39" s="25">
-        <f>IF(I39=0,"",AL39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:AJ39))/I39)</f>
         <v/>
       </c>
       <c r="AO39" s="26" t="n"/>
@@ -3365,15 +3400,15 @@
       <c r="AJ40" s="21" t="n"/>
       <c r="AK40" s="21" t="n"/>
       <c r="AL40" s="24">
-        <f>SUM(M40:AJ40)</f>
+        <f>H40+SUM(M40:AJ40)</f>
         <v/>
       </c>
       <c r="AM40" s="24">
-        <f>I40-AL40</f>
+        <f>I40-H40-SUM(M40:AJ40)</f>
         <v/>
       </c>
       <c r="AN40" s="25">
-        <f>IF(I40=0,"",AL40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:AJ40))/I40)</f>
         <v/>
       </c>
       <c r="AO40" s="26" t="n"/>
@@ -3426,15 +3461,15 @@
       <c r="AJ41" s="21" t="n"/>
       <c r="AK41" s="21" t="n"/>
       <c r="AL41" s="24">
-        <f>SUM(M41:AJ41)</f>
+        <f>H41+SUM(M41:AJ41)</f>
         <v/>
       </c>
       <c r="AM41" s="24">
-        <f>I41-AL41</f>
+        <f>I41-H41-SUM(M41:AJ41)</f>
         <v/>
       </c>
       <c r="AN41" s="25">
-        <f>IF(I41=0,"",AL41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:AJ41))/I41)</f>
         <v/>
       </c>
       <c r="AO41" s="26" t="n"/>
@@ -3487,15 +3522,15 @@
       <c r="AJ42" s="21" t="n"/>
       <c r="AK42" s="21" t="n"/>
       <c r="AL42" s="24">
-        <f>SUM(M42:AJ42)</f>
+        <f>H42+SUM(M42:AJ42)</f>
         <v/>
       </c>
       <c r="AM42" s="24">
-        <f>I42-AL42</f>
+        <f>I42-H42-SUM(M42:AJ42)</f>
         <v/>
       </c>
       <c r="AN42" s="25">
-        <f>IF(I42=0,"",AL42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:AJ42))/I42)</f>
         <v/>
       </c>
       <c r="AO42" s="26" t="n"/>
@@ -3548,15 +3583,15 @@
       <c r="AJ43" s="21" t="n"/>
       <c r="AK43" s="21" t="n"/>
       <c r="AL43" s="24">
-        <f>SUM(M43:AJ43)</f>
+        <f>H43+SUM(M43:AJ43)</f>
         <v/>
       </c>
       <c r="AM43" s="24">
-        <f>I43-AL43</f>
+        <f>I43-H43-SUM(M43:AJ43)</f>
         <v/>
       </c>
       <c r="AN43" s="25">
-        <f>IF(I43=0,"",AL43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:AJ43))/I43)</f>
         <v/>
       </c>
       <c r="AO43" s="26" t="n"/>
@@ -3609,15 +3644,15 @@
       <c r="AJ44" s="21" t="n"/>
       <c r="AK44" s="21" t="n"/>
       <c r="AL44" s="24">
-        <f>SUM(M44:AJ44)</f>
+        <f>H44+SUM(M44:AJ44)</f>
         <v/>
       </c>
       <c r="AM44" s="24">
-        <f>I44-AL44</f>
+        <f>I44-H44-SUM(M44:AJ44)</f>
         <v/>
       </c>
       <c r="AN44" s="25">
-        <f>IF(I44=0,"",AL44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:AJ44))/I44)</f>
         <v/>
       </c>
       <c r="AO44" s="26" t="n"/>
@@ -3670,15 +3705,15 @@
       <c r="AJ45" s="21" t="n"/>
       <c r="AK45" s="21" t="n"/>
       <c r="AL45" s="24">
-        <f>SUM(M45:AJ45)</f>
+        <f>H45+SUM(M45:AJ45)</f>
         <v/>
       </c>
       <c r="AM45" s="24">
-        <f>I45-AL45</f>
+        <f>I45-H45-SUM(M45:AJ45)</f>
         <v/>
       </c>
       <c r="AN45" s="25">
-        <f>IF(I45=0,"",AL45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:AJ45))/I45)</f>
         <v/>
       </c>
       <c r="AO45" s="26" t="n"/>
@@ -3731,15 +3766,15 @@
       <c r="AJ46" s="21" t="n"/>
       <c r="AK46" s="21" t="n"/>
       <c r="AL46" s="24">
-        <f>SUM(M46:AJ46)</f>
+        <f>H46+SUM(M46:AJ46)</f>
         <v/>
       </c>
       <c r="AM46" s="24">
-        <f>I46-AL46</f>
+        <f>I46-H46-SUM(M46:AJ46)</f>
         <v/>
       </c>
       <c r="AN46" s="25">
-        <f>IF(I46=0,"",AL46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:AJ46))/I46)</f>
         <v/>
       </c>
       <c r="AO46" s="26" t="n"/>
@@ -3792,15 +3827,15 @@
       <c r="AJ47" s="21" t="n"/>
       <c r="AK47" s="21" t="n"/>
       <c r="AL47" s="24">
-        <f>SUM(M47:AJ47)</f>
+        <f>H47+SUM(M47:AJ47)</f>
         <v/>
       </c>
       <c r="AM47" s="24">
-        <f>I47-AL47</f>
+        <f>I47-H47-SUM(M47:AJ47)</f>
         <v/>
       </c>
       <c r="AN47" s="25">
-        <f>IF(I47=0,"",AL47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:AJ47))/I47)</f>
         <v/>
       </c>
       <c r="AO47" s="26" t="n"/>
@@ -3853,15 +3888,15 @@
       <c r="AJ48" s="21" t="n"/>
       <c r="AK48" s="21" t="n"/>
       <c r="AL48" s="24">
-        <f>SUM(M48:AJ48)</f>
+        <f>H48+SUM(M48:AJ48)</f>
         <v/>
       </c>
       <c r="AM48" s="24">
-        <f>I48-AL48</f>
+        <f>I48-H48-SUM(M48:AJ48)</f>
         <v/>
       </c>
       <c r="AN48" s="25">
-        <f>IF(I48=0,"",AL48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:AJ48))/I48)</f>
         <v/>
       </c>
       <c r="AO48" s="26" t="n"/>
@@ -3914,15 +3949,15 @@
       <c r="AJ49" s="21" t="n"/>
       <c r="AK49" s="21" t="n"/>
       <c r="AL49" s="24">
-        <f>SUM(M49:AJ49)</f>
+        <f>H49+SUM(M49:AJ49)</f>
         <v/>
       </c>
       <c r="AM49" s="24">
-        <f>I49-AL49</f>
+        <f>I49-H49-SUM(M49:AJ49)</f>
         <v/>
       </c>
       <c r="AN49" s="25">
-        <f>IF(I49=0,"",AL49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:AJ49))/I49)</f>
         <v/>
       </c>
       <c r="AO49" s="26" t="n"/>
@@ -3975,15 +4010,15 @@
       <c r="AJ50" s="21" t="n"/>
       <c r="AK50" s="21" t="n"/>
       <c r="AL50" s="24">
-        <f>SUM(M50:AJ50)</f>
+        <f>H50+SUM(M50:AJ50)</f>
         <v/>
       </c>
       <c r="AM50" s="24">
-        <f>I50-AL50</f>
+        <f>I50-H50-SUM(M50:AJ50)</f>
         <v/>
       </c>
       <c r="AN50" s="25">
-        <f>IF(I50=0,"",AL50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:AJ50))/I50)</f>
         <v/>
       </c>
       <c r="AO50" s="26" t="n"/>
@@ -4036,15 +4071,15 @@
       <c r="AJ51" s="21" t="n"/>
       <c r="AK51" s="21" t="n"/>
       <c r="AL51" s="24">
-        <f>SUM(M51:AJ51)</f>
+        <f>H51+SUM(M51:AJ51)</f>
         <v/>
       </c>
       <c r="AM51" s="24">
-        <f>I51-AL51</f>
+        <f>I51-H51-SUM(M51:AJ51)</f>
         <v/>
       </c>
       <c r="AN51" s="25">
-        <f>IF(I51=0,"",AL51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:AJ51))/I51)</f>
         <v/>
       </c>
       <c r="AO51" s="26" t="n"/>
